--- a/output/pdf_financials_xlsx/PRQ.xlsx
+++ b/output/pdf_financials_xlsx/PRQ.xlsx
@@ -5351,22 +5351,22 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005496</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>0.004917</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.001794</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>1.954</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.000452</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.00161</v>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001224</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.004422</v>
       </c>
       <c r="K118" s="1" t="inlineStr">
         <is>
@@ -21002,7 +21002,11 @@
           <t>Exploration and evaluation expense (note 6)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E236" s="5" t="n">
         <v>0.001158</v>
       </c>
@@ -22634,7 +22638,11 @@
           <t>Exploration and evaluation asset expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>-0.006654</v>
       </c>

--- a/output/pdf_financials_xlsx/PRQ.xlsx
+++ b/output/pdf_financials_xlsx/PRQ.xlsx
@@ -2169,34 +2169,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.019524</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.00028</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000256</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004928</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000375</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2243,34 +2243,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.019524</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.00028</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000256</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004928</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000375</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="37">
@@ -2687,34 +2687,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.035175</v>
+        <v>0.015651</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016321</v>
+        <v>0.015087</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001413</v>
+        <v>0.001133</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.617</v>
+        <v>3.593</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.008146</v>
+        <v>0.008083</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001584</v>
+        <v>0.001328</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005878</v>
+        <v>0.00095</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006404</v>
+        <v>0.006364</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.013523</v>
+        <v>0.013148</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.00603</v>
+        <v>0.005962</v>
       </c>
     </row>
     <row r="49">
@@ -5609,10 +5609,10 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003464</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000381</v>
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000451</v>
       </c>
       <c r="K124" s="1" t="inlineStr">
         <is>
@@ -5650,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003464</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000381</v>
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>0.025</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000451</v>
       </c>
       <c r="K125" s="1" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -22062,7 +22062,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
